--- a/output/roomself_excel/2606.xlsx
+++ b/output/roomself_excel/2606.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>123917</v>
+        <v>208486</v>
       </c>
       <c r="D2" t="n">
-        <v>3016</v>
+        <v>4140</v>
       </c>
       <c r="E2" t="n">
-        <v>418</v>
+        <v>407</v>
       </c>
       <c r="F2" t="n">
-        <v>326</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>18624</v>
+        <v>253435</v>
       </c>
       <c r="D3" t="n">
-        <v>1160</v>
+        <v>4300</v>
       </c>
       <c r="E3" t="n">
-        <v>96</v>
+        <v>549</v>
       </c>
       <c r="F3" t="n">
-        <v>21</v>
+        <v>503</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>45590</v>
+        <v>123917</v>
       </c>
       <c r="D4" t="n">
-        <v>1716</v>
+        <v>3016</v>
       </c>
       <c r="E4" t="n">
-        <v>235</v>
+        <v>418</v>
       </c>
       <c r="F4" t="n">
-        <v>21</v>
+        <v>317</v>
       </c>
     </row>
     <row r="5">
@@ -532,17 +532,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>30652</v>
+        <v>127874</v>
       </c>
       <c r="D5" t="n">
-        <v>1408</v>
+        <v>3196</v>
       </c>
       <c r="E5" t="n">
-        <v>158</v>
+        <v>341</v>
       </c>
       <c r="F5" t="n">
         <v>21</v>
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>253435</v>
+        <v>156815</v>
       </c>
       <c r="D6" t="n">
-        <v>4300</v>
+        <v>3168</v>
       </c>
       <c r="E6" t="n">
-        <v>576</v>
+        <v>395</v>
       </c>
       <c r="F6" t="n">
-        <v>503</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>268776</v>
+        <v>52896</v>
       </c>
       <c r="D7" t="n">
-        <v>5992</v>
+        <v>2000</v>
       </c>
       <c r="E7" t="n">
-        <v>944</v>
+        <v>152</v>
       </c>
       <c r="F7" t="n">
-        <v>910</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8">
@@ -598,17 +598,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>127874</v>
+        <v>18624</v>
       </c>
       <c r="D8" t="n">
-        <v>3196</v>
+        <v>1160</v>
       </c>
       <c r="E8" t="n">
-        <v>341</v>
+        <v>96</v>
       </c>
       <c r="F8" t="n">
         <v>21</v>
@@ -624,13 +624,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3700</v>
+        <v>45590</v>
       </c>
       <c r="D9" t="n">
-        <v>496</v>
+        <v>1716</v>
       </c>
       <c r="E9" t="n">
-        <v>38</v>
+        <v>235</v>
       </c>
       <c r="F9" t="n">
         <v>21</v>
@@ -646,13 +646,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8732</v>
+        <v>30652</v>
       </c>
       <c r="D10" t="n">
-        <v>768</v>
+        <v>1408</v>
       </c>
       <c r="E10" t="n">
-        <v>118</v>
+        <v>158</v>
       </c>
       <c r="F10" t="n">
         <v>21</v>
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>156815</v>
+        <v>60290</v>
       </c>
       <c r="D11" t="n">
-        <v>3168</v>
+        <v>2324</v>
       </c>
       <c r="E11" t="n">
-        <v>797</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>395</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -686,19 +686,41 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>52896</v>
+        <v>3700</v>
       </c>
       <c r="D12" t="n">
-        <v>2000</v>
+        <v>496</v>
       </c>
       <c r="E12" t="n">
-        <v>152</v>
+        <v>38</v>
       </c>
       <c r="F12" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>8732</v>
+      </c>
+      <c r="D13" t="n">
+        <v>768</v>
+      </c>
+      <c r="E13" t="n">
+        <v>118</v>
+      </c>
+      <c r="F13" t="n">
         <v>21</v>
       </c>
     </row>

--- a/output/roomself_excel/2606.xlsx
+++ b/output/roomself_excel/2606.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,12 +495,20 @@
       <c r="D2" t="n">
         <v>4140</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>407</v>
       </c>
-      <c r="F2" t="n">
-        <v>21</v>
-      </c>
+      <c r="G2" t="n">
+        <v>21</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,11 +525,27 @@
       <c r="D3" t="n">
         <v>4300</v>
       </c>
-      <c r="E3" t="n">
-        <v>549</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>503</v>
+        <v>1060</v>
+      </c>
+      <c r="G3" t="n">
+        <v>21</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>461</v>
+      </c>
+      <c r="J3" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="4">
@@ -519,11 +563,27 @@
       <c r="D4" t="n">
         <v>3016</v>
       </c>
-      <c r="E4" t="n">
-        <v>418</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>317</v>
+        <v>397</v>
+      </c>
+      <c r="G4" t="n">
+        <v>21</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>296</v>
+      </c>
+      <c r="J4" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="5">
@@ -541,12 +601,20 @@
       <c r="D5" t="n">
         <v>3196</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>341</v>
       </c>
-      <c r="F5" t="n">
-        <v>21</v>
-      </c>
+      <c r="G5" t="n">
+        <v>21</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,11 +631,27 @@
       <c r="D6" t="n">
         <v>3168</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>395</v>
       </c>
-      <c r="F6" t="n">
-        <v>21</v>
+      <c r="G6" t="n">
+        <v>21</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>397</v>
+      </c>
+      <c r="J6" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="7">
@@ -585,11 +669,27 @@
       <c r="D7" t="n">
         <v>2000</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>152</v>
       </c>
-      <c r="F7" t="n">
-        <v>21</v>
+      <c r="G7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>348</v>
+      </c>
+      <c r="J7" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="8">
@@ -607,12 +707,20 @@
       <c r="D8" t="n">
         <v>1160</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>96</v>
       </c>
-      <c r="F8" t="n">
-        <v>21</v>
-      </c>
+      <c r="G8" t="n">
+        <v>21</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +737,20 @@
       <c r="D9" t="n">
         <v>1716</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>235</v>
       </c>
-      <c r="F9" t="n">
-        <v>21</v>
-      </c>
+      <c r="G9" t="n">
+        <v>21</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +767,20 @@
       <c r="D10" t="n">
         <v>1408</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
         <v>158</v>
       </c>
-      <c r="F10" t="n">
-        <v>21</v>
-      </c>
+      <c r="G10" t="n">
+        <v>21</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +797,12 @@
       <c r="D11" t="n">
         <v>2324</v>
       </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +819,20 @@
       <c r="D12" t="n">
         <v>496</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
         <v>38</v>
       </c>
-      <c r="F12" t="n">
-        <v>21</v>
-      </c>
+      <c r="G12" t="n">
+        <v>21</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +849,20 @@
       <c r="D13" t="n">
         <v>768</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
         <v>118</v>
       </c>
-      <c r="F13" t="n">
-        <v>21</v>
-      </c>
+      <c r="G13" t="n">
+        <v>21</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
